--- a/mlef_pipeline/results/OS_24/HIGH_PDL1/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_24/HIGH_PDL1/training_summary.xlsx
@@ -552,34 +552,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.683942731277533</v>
+        <v>0.6820925110132159</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06557413473311446</v>
+        <v>0.06596980915247919</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5810828122479249</v>
+        <v>0.5695463754538317</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1275817583035329</v>
+        <v>0.1308991681944261</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5666218762549038</v>
+        <v>0.595838531159632</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1377044194072659</v>
+        <v>0.172641739622133</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6705804484163492</v>
+        <v>0.6487507028827421</v>
       </c>
       <c r="I2" t="n">
-        <v>0.215969018802263</v>
+        <v>0.2205354439112355</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7901960784313724</v>
+        <v>0.7941176470588234</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1454533585814919</v>
+        <v>0.1422884762985884</v>
       </c>
       <c r="L2" t="n">
         <v>0.7306346826586707</v>
@@ -591,10 +591,10 @@
         <v>0.8529411764705882</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6380494505494505</v>
+        <v>0.6270604395604396</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1440946895071603</v>
+        <v>0.1447840042348248</v>
       </c>
       <c r="Q2" t="n">
         <v>0.3635966826713226</v>
@@ -993,7 +993,7 @@
         <v>0.5962254120148858</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1140364365074725</v>
+        <v>0.1140364365074726</v>
       </c>
       <c r="D8" t="n">
         <v>0.3072744052477261</v>
